--- a/Check.xlsx
+++ b/Check.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="40">
   <si>
     <t>Группа проверок/модуль</t>
   </si>
@@ -109,6 +109,33 @@
   </si>
   <si>
     <t>Раскрытие цитаты</t>
+  </si>
+  <si>
+    <t>Ввод невалидных данных в поле логина</t>
+  </si>
+  <si>
+    <t>Переполнение  поля логина</t>
+  </si>
+  <si>
+    <t>Скрытие  новости</t>
+  </si>
+  <si>
+    <t>Ввод невалидных данных при фильрации новостей</t>
+  </si>
+  <si>
+    <t>Переполнение полей данных при фильрации новостей</t>
+  </si>
+  <si>
+    <t>Ввод невалидных данных при редактировании новостей</t>
+  </si>
+  <si>
+    <t>Переполнение полей данных при редактировании новостей</t>
+  </si>
+  <si>
+    <t>Переполнение полей данных при создание новости</t>
+  </si>
+  <si>
+    <t>Ввод невалидных данных присоздание новости</t>
   </si>
 </sst>
 </file>
@@ -335,17 +362,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -359,13 +380,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -387,6 +414,34 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp100.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp101.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp102.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp103.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp104.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp105.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp106.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -395,7 +450,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
@@ -403,7 +458,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,7 +466,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -419,7 +474,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -431,7 +486,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,7 +494,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
@@ -447,7 +502,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,7 +510,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
@@ -463,7 +518,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,7 +530,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
@@ -483,7 +538,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
@@ -491,7 +546,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
@@ -499,7 +554,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
@@ -507,7 +562,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
@@ -522,23 +577,259 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp86.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp87.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp88.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp89.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp90.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp91.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp92.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp93.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp94.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp95.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp96.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp97.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp98.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp99.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
@@ -714,13 +1005,13 @@
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
           <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -755,13 +1046,13 @@
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
           <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -770,170 +1061,6 @@
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1136"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1137" name="Check Box 113" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1137"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1138" name="Check Box 114" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1138"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1139" name="Check Box 115" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1139"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1140" name="Check Box 116" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1140"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -971,10 +1098,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1141" name="Check Box 117" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1141"/>
+            <xdr:cNvPr id="1137" name="Check Box 113" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1137"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1012,92 +1139,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1142" name="Check Box 118" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1142"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>22860</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1143" name="Check Box 119" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1143"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>22860</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1144" name="Check Box 120" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1144"/>
+            <xdr:cNvPr id="1138" name="Check Box 114" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1138"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1135,10 +1180,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1145" name="Check Box 121" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1145"/>
+            <xdr:cNvPr id="1139" name="Check Box 115" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1139"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1176,10 +1221,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1146" name="Check Box 122" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1146"/>
+            <xdr:cNvPr id="1140" name="Check Box 116" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1140"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1217,10 +1262,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1147" name="Check Box 123" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1147"/>
+            <xdr:cNvPr id="1141" name="Check Box 117" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1141"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1258,10 +1303,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1148" name="Check Box 124" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1148"/>
+            <xdr:cNvPr id="1142" name="Check Box 118" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1142"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1295,14 +1340,14 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>624840</xdr:colOff>
           <xdr:row>11</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1149" name="Check Box 125" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1149"/>
+            <xdr:cNvPr id="1143" name="Check Box 119" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1143"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1336,14 +1381,14 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>624840</xdr:colOff>
           <xdr:row>11</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1150" name="Check Box 126" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1150"/>
+            <xdr:cNvPr id="1144" name="Check Box 120" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1144"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1381,10 +1426,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1151" name="Check Box 127" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1151"/>
+            <xdr:cNvPr id="1145" name="Check Box 121" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1145"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1422,174 +1467,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1152" name="Check Box 128" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1152"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1153" name="Check Box 129" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1153"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1154" name="Check Box 130" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1155" name="Check Box 131" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1155"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1156" name="Check Box 132" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1156"/>
+            <xdr:cNvPr id="1146" name="Check Box 122" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1146"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1627,10 +1508,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1157" name="Check Box 133" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1157"/>
+            <xdr:cNvPr id="1147" name="Check Box 123" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1147"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1668,10 +1549,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1158" name="Check Box 134" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1158"/>
+            <xdr:cNvPr id="1148" name="Check Box 124" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1148"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1709,10 +1590,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1159" name="Check Box 135" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1159"/>
+            <xdr:cNvPr id="1149" name="Check Box 125" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1149"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1750,174 +1631,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1160" name="Check Box 136" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1160"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1161" name="Check Box 137" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1161"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1162" name="Check Box 138" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1162"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1163" name="Check Box 139" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1163"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1164" name="Check Box 140" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1164"/>
+            <xdr:cNvPr id="1150" name="Check Box 126" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1150"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1955,10 +1672,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1165" name="Check Box 141" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1165"/>
+            <xdr:cNvPr id="1151" name="Check Box 127" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1151"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1996,10 +1713,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1166" name="Check Box 142" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1166"/>
+            <xdr:cNvPr id="1152" name="Check Box 128" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1152"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2037,10 +1754,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1167" name="Check Box 143" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1167"/>
+            <xdr:cNvPr id="1153" name="Check Box 129" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1153"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2078,10 +1795,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1168" name="Check Box 144" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1168"/>
+            <xdr:cNvPr id="1154" name="Check Box 130" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1154"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2115,6 +1832,580 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>624840</xdr:colOff>
           <xdr:row>21</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1155" name="Check Box 131" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1155"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1156" name="Check Box 132" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1156"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1157" name="Check Box 133" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1157"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1158" name="Check Box 134" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1158"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1159" name="Check Box 135" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1159"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1160" name="Check Box 136" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1160"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1161" name="Check Box 137" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1161"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1162" name="Check Box 138" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1162"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1163" name="Check Box 139" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1163"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1164" name="Check Box 140" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1164"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1165" name="Check Box 141" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1165"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1166" name="Check Box 142" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1166"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1167" name="Check Box 143" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1167"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1168" name="Check Box 144" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1168"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>624840</xdr:colOff>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>83820</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2149,13 +2440,13 @@
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>198120</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
           <xdr:colOff>624840</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>83820</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2181,6 +2472,2382 @@
         </xdr:sp>
         <xdr:clientData/>
       </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1171" name="Check Box 147" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1171"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1172" name="Check Box 148" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1172"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1173" name="Check Box 149" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1173"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1174" name="Check Box 150" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1174"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1175" name="Check Box 151" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1175"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1176" name="Check Box 152" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1176"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1177" name="Check Box 153" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1177"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1178" name="Check Box 154" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1178"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1179" name="Check Box 155" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1179"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1180" name="Check Box 156" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1180"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1181" name="Check Box 157" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1181"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1182" name="Check Box 158" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1182"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1183" name="Check Box 159" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1183"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1184" name="Check Box 160" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1184"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1185" name="Check Box 161" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1185"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1186" name="Check Box 162" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1186"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1187" name="Check Box 163" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1187"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1188" name="Check Box 164" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1188"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1189" name="Check Box 165" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1189"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1190" name="Check Box 166" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1190"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1191" name="Check Box 167" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1191"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1192" name="Check Box 168" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1192"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1193" name="Check Box 169" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1193"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1194" name="Check Box 170" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1194"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1195" name="Check Box 171" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1195"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1196" name="Check Box 172" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1196"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1197" name="Check Box 173" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1197"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1198" name="Check Box 174" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1198"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1199" name="Check Box 175" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1199"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1200" name="Check Box 176" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1200"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1201" name="Check Box 177" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1201"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1202" name="Check Box 178" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1202"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1203" name="Check Box 179" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1203"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1204" name="Check Box 180" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1204"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1205" name="Check Box 181" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1205"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1206" name="Check Box 182" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1206"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1207" name="Check Box 183" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1207"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1208" name="Check Box 184" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1208"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1209" name="Check Box 185" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1209"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1210" name="Check Box 186" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1210"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1211" name="Check Box 187" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1211"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1212" name="Check Box 188" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1212"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1213" name="Check Box 189" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1213"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1214" name="Check Box 190" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1214"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1215" name="Check Box 191" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1215"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1216" name="Check Box 192" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1216"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1217" name="Check Box 193" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1217"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1218" name="Check Box 194" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1218"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1219" name="Check Box 195" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1219"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1220" name="Check Box 196" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1220"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1221" name="Check Box 197" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1221"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1222" name="Check Box 198" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1222"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1223" name="Check Box 199" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1223"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1224" name="Check Box 200" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1224"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1225" name="Check Box 201" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1225"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1226" name="Check Box 202" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1226"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1227" name="Check Box 203" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1227"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1228" name="Check Box 204" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1228"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1229" name="Check Box 205" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1229"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1230" name="Check Box 206" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1230"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1231" name="Check Box 207" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1231"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1232" name="Check Box 208" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1232"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1233" name="Check Box 209" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1233"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1234" name="Check Box 210" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1234"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1235" name="Check Box 211" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1235"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="426720" cy="266700"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1236" name="Check Box 212" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1236"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
@@ -2475,7 +5142,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.5546875" customWidth="1"/>
@@ -2491,220 +5158,310 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="11"/>
+      <c r="D2" s="9"/>
     </row>
     <row r="3" spans="1:4" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="13"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="13"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:4" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:4" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="12"/>
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D6" s="9"/>
     </row>
-    <row r="5" spans="1:4" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="12" t="s">
+    <row r="7" spans="1:4" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D7" s="9"/>
     </row>
-    <row r="6" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="13"/>
-      <c r="B6" s="3" t="s">
+    <row r="8" spans="1:4" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="11"/>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="11"/>
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D9" s="9"/>
     </row>
-    <row r="7" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="13"/>
-      <c r="B7" s="3" t="s">
+    <row r="10" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="11"/>
+      <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D10" s="9"/>
     </row>
-    <row r="8" spans="1:4" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="13"/>
-      <c r="B8" s="3" t="s">
+    <row r="11" spans="1:4" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="11"/>
+      <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D11" s="9"/>
     </row>
-    <row r="9" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="13"/>
-      <c r="B9" s="3" t="s">
+    <row r="12" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="11"/>
+      <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D12" s="9"/>
     </row>
-    <row r="10" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="13"/>
-      <c r="B10" s="3" t="s">
+    <row r="13" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="11"/>
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="11"/>
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="11"/>
+      <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D15" s="9"/>
     </row>
-    <row r="11" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="13"/>
-      <c r="B11" s="3" t="s">
+    <row r="16" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="11"/>
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D16" s="9"/>
     </row>
-    <row r="12" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="13"/>
-      <c r="B12" s="3" t="s">
+    <row r="17" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="11"/>
+      <c r="B17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="11"/>
+      <c r="B18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="11"/>
+      <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D19" s="9"/>
     </row>
-    <row r="13" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="13"/>
-      <c r="B13" s="3" t="s">
+    <row r="20" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="11"/>
+      <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D20" s="9"/>
     </row>
-    <row r="14" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="13"/>
-      <c r="B14" s="3" t="s">
+    <row r="21" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="11"/>
+      <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="11"/>
+      <c r="D21" s="9"/>
     </row>
-    <row r="15" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="14"/>
-      <c r="B15" s="3" t="s">
+    <row r="22" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="11"/>
+      <c r="B22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="11"/>
+      <c r="B23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="12"/>
+      <c r="B24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D24" s="9"/>
     </row>
-    <row r="16" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="12" t="s">
+    <row r="25" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D25" s="9"/>
     </row>
-    <row r="17" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="13"/>
-      <c r="B17" s="3" t="s">
+    <row r="26" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="11"/>
+      <c r="B26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D26" s="9"/>
     </row>
-    <row r="18" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
+    <row r="27" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C27" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D27" s="9"/>
     </row>
-    <row r="19" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
+    <row r="28" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C28" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D28" s="9"/>
     </row>
-    <row r="20" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="7" t="s">
+    <row r="29" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D29" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A15"/>
-    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A24"/>
+    <mergeCell ref="A25:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2809,6 +5566,842 @@
                   <from>
                     <xdr:col>3</xdr:col>
                     <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1136" r:id="rId9" name="Check Box 112">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1137" r:id="rId10" name="Check Box 113">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1138" r:id="rId11" name="Check Box 114">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1139" r:id="rId12" name="Check Box 115">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1140" r:id="rId13" name="Check Box 116">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1141" r:id="rId14" name="Check Box 117">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1142" r:id="rId15" name="Check Box 118">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1143" r:id="rId16" name="Check Box 119">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1144" r:id="rId17" name="Check Box 120">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1145" r:id="rId18" name="Check Box 121">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1146" r:id="rId19" name="Check Box 122">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1147" r:id="rId20" name="Check Box 123">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>14</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1148" r:id="rId21" name="Check Box 124">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>14</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1149" r:id="rId22" name="Check Box 125">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1150" r:id="rId23" name="Check Box 126">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1151" r:id="rId24" name="Check Box 127">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1152" r:id="rId25" name="Check Box 128">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1153" r:id="rId26" name="Check Box 129">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1154" r:id="rId27" name="Check Box 130">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1155" r:id="rId28" name="Check Box 131">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1156" r:id="rId29" name="Check Box 132">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1157" r:id="rId30" name="Check Box 133">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1158" r:id="rId31" name="Check Box 134">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1159" r:id="rId32" name="Check Box 135">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1160" r:id="rId33" name="Check Box 136">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1161" r:id="rId34" name="Check Box 137">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1162" r:id="rId35" name="Check Box 138">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1163" r:id="rId36" name="Check Box 139">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1164" r:id="rId37" name="Check Box 140">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1165" r:id="rId38" name="Check Box 141">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1166" r:id="rId39" name="Check Box 142">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1167" r:id="rId40" name="Check Box 143">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1168" r:id="rId41" name="Check Box 144">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1169" r:id="rId42" name="Check Box 145">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>83820</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1170" r:id="rId43" name="Check Box 146">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>83820</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1171" r:id="rId44" name="Check Box 147">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1172" r:id="rId45" name="Check Box 148">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1173" r:id="rId46" name="Check Box 149">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>3</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
@@ -2825,7 +6418,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId9" name="Check Box 112">
+            <control shapeId="1174" r:id="rId47" name="Check Box 150">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -2847,29 +6440,161 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId10" name="Check Box 113">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
+            <control shapeId="1175" r:id="rId48" name="Check Box 151">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>4</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1176" r:id="rId49" name="Check Box 152">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1177" r:id="rId50" name="Check Box 153">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1178" r:id="rId51" name="Check Box 154">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1179" r:id="rId52" name="Check Box 155">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1180" r:id="rId53" name="Check Box 156">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1181" r:id="rId54" name="Check Box 157">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>4</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
                     <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId11" name="Check Box 114">
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1182" r:id="rId55" name="Check Box 158">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -2882,66 +6607,88 @@
                     <xdr:col>3</xdr:col>
                     <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId12" name="Check Box 115">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1183" r:id="rId56" name="Check Box 159">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1184" r:id="rId57" name="Check Box 160">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1185" r:id="rId58" name="Check Box 161">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId13" name="Check Box 116">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1186" r:id="rId59" name="Check Box 162">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId14" name="Check Box 117">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>6</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
@@ -2957,29 +6704,29 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId15" name="Check Box 118">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
+            <control shapeId="1187" r:id="rId60" name="Check Box 163">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId16" name="Check Box 119">
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1188" r:id="rId61" name="Check Box 164">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -2992,170 +6739,60 @@
                     <xdr:col>3</xdr:col>
                     <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>22860</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId17" name="Check Box 120">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>22860</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId18" name="Check Box 121">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId19" name="Check Box 122">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId20" name="Check Box 123">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId21" name="Check Box 124">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId22" name="Check Box 125">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1189" r:id="rId62" name="Check Box 165">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>11</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId23" name="Check Box 126">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1190" r:id="rId63" name="Check Box 166">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>11</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId24" name="Check Box 127">
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1191" r:id="rId64" name="Check Box 167">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3177,7 +6814,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId25" name="Check Box 128">
+            <control shapeId="1192" r:id="rId65" name="Check Box 168">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3199,13 +6836,101 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId26" name="Check Box 129">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
+            <control shapeId="1193" r:id="rId66" name="Check Box 169">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>12</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1194" r:id="rId67" name="Check Box 170">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1195" r:id="rId68" name="Check Box 171">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1196" r:id="rId69" name="Check Box 172">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1197" r:id="rId70" name="Check Box 173">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
@@ -3221,7 +6946,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId27" name="Check Box 130">
+            <control shapeId="1198" r:id="rId71" name="Check Box 174">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3243,13 +6968,233 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1155" r:id="rId28" name="Check Box 131">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
+            <control shapeId="1199" r:id="rId72" name="Check Box 175">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1200" r:id="rId73" name="Check Box 176">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1201" r:id="rId74" name="Check Box 177">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1202" r:id="rId75" name="Check Box 178">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1203" r:id="rId76" name="Check Box 179">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1204" r:id="rId77" name="Check Box 180">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1205" r:id="rId78" name="Check Box 181">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1206" r:id="rId79" name="Check Box 182">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1207" r:id="rId80" name="Check Box 183">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1208" r:id="rId81" name="Check Box 184">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1209" r:id="rId82" name="Check Box 185">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>13</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
@@ -3265,7 +7210,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1156" r:id="rId29" name="Check Box 132">
+            <control shapeId="1210" r:id="rId83" name="Check Box 186">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3287,95 +7232,95 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1157" r:id="rId30" name="Check Box 133">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
+            <control shapeId="1211" r:id="rId84" name="Check Box 187">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>14</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1158" r:id="rId31" name="Check Box 134">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1212" r:id="rId85" name="Check Box 188">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>14</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1159" r:id="rId32" name="Check Box 135">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1213" r:id="rId86" name="Check Box 189">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>16</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1160" r:id="rId33" name="Check Box 136">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1214" r:id="rId87" name="Check Box 190">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>16</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1161" r:id="rId34" name="Check Box 137">
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1215" r:id="rId88" name="Check Box 191">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3397,7 +7342,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1162" r:id="rId35" name="Check Box 138">
+            <control shapeId="1216" r:id="rId89" name="Check Box 192">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3419,13 +7364,101 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1163" r:id="rId36" name="Check Box 139">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
+            <control shapeId="1217" r:id="rId90" name="Check Box 193">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>17</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1218" r:id="rId91" name="Check Box 194">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1219" r:id="rId92" name="Check Box 195">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1220" r:id="rId93" name="Check Box 196">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1221" r:id="rId94" name="Check Box 197">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>17</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
@@ -3441,7 +7474,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1164" r:id="rId37" name="Check Box 140">
+            <control shapeId="1222" r:id="rId95" name="Check Box 198">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3463,130 +7496,306 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1165" r:id="rId38" name="Check Box 141">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
+            <control shapeId="1223" r:id="rId96" name="Check Box 199">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>18</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1166" r:id="rId39" name="Check Box 142">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1224" r:id="rId97" name="Check Box 200">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
                     <xdr:row>18</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1167" r:id="rId40" name="Check Box 143">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1168" r:id="rId41" name="Check Box 144">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1169" r:id="rId42" name="Check Box 145">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1225" r:id="rId98" name="Check Box 201">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>83820</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1170" r:id="rId43" name="Check Box 146">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>198120</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1226" r:id="rId99" name="Check Box 202">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>83820</xdr:rowOff>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1227" r:id="rId100" name="Check Box 203">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1228" r:id="rId101" name="Check Box 204">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1229" r:id="rId102" name="Check Box 205">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1230" r:id="rId103" name="Check Box 206">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1231" r:id="rId104" name="Check Box 207">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1232" r:id="rId105" name="Check Box 208">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1233" r:id="rId106" name="Check Box 209">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1234" r:id="rId107" name="Check Box 210">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1235" r:id="rId108" name="Check Box 211">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1236" r:id="rId109" name="Check Box 212">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>624840</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
